--- a/Templates/UomConversionsSchema.xlsx
+++ b/Templates/UomConversionsSchema.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\uploaddata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitrepos\GMPPro20DataUpload\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F41C3B2-F475-4D4B-9C14-AC2509C41D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA82A85B-D243-4E8C-8412-9B66218B7D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9A0E982F-1D0A-437F-BDA7-ED9E8C087AEA}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$59</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="43">
   <si>
     <t>Property</t>
   </si>
@@ -144,7 +144,19 @@
     <t>uomConversions</t>
   </si>
   <si>
-    <t>decimal</t>
+    <t>settings</t>
+  </si>
+  <si>
+    <t>basicInfoID</t>
+  </si>
+  <si>
+    <t>consume</t>
+  </si>
+  <si>
+    <t>systemData.basicInfoID</t>
+  </si>
+  <si>
+    <t>systemData.requestCode</t>
   </si>
 </sst>
 </file>
@@ -496,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2691CE0-5D18-450E-B7A3-EA23A82B1B89}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
@@ -574,7 +586,10 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>38</v>
+      </c>
+      <c r="G3" t="s">
+        <v>24</v>
       </c>
       <c r="H3" t="s">
         <v>24</v>
@@ -743,7 +758,7 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -813,6 +828,98 @@
       </c>
       <c r="H14" t="s">
         <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" t="s">
+        <v>39</v>
+      </c>
+      <c r="C15" t="s">
+        <v>22</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" t="s">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" t="s">
+        <v>40</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" t="s">
+        <v>20</v>
+      </c>
+      <c r="C17" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>9</v>
+      </c>
+      <c r="H17" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="H18" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/Templates/UomConversionsSchema.xlsx
+++ b/Templates/UomConversionsSchema.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gitrepos\GMPPro20DataUpload\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA82A85B-D243-4E8C-8412-9B66218B7D89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F44FE9F-C0FD-4634-A99D-998845161991}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9A0E982F-1D0A-437F-BDA7-ED9E8C087AEA}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -157,6 +157,15 @@
   </si>
   <si>
     <t>systemData.requestCode</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>formula</t>
+  </si>
+  <si>
+    <t>now()</t>
   </si>
 </sst>
 </file>
@@ -508,7 +517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2691CE0-5D18-450E-B7A3-EA23A82B1B89}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.81640625" bestFit="1" customWidth="1"/>
@@ -520,7 +529,7 @@
     <col min="8" max="8" width="35.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -545,8 +554,11 @@
       <c r="H1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -572,7 +584,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -595,7 +607,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -618,7 +630,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -638,7 +650,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -658,7 +670,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -678,7 +690,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -704,7 +716,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -727,7 +739,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -750,7 +762,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>28</v>
       </c>
@@ -758,7 +770,7 @@
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -770,7 +782,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>28</v>
       </c>
@@ -789,8 +801,11 @@
       <c r="H12" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="I12" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>28</v>
       </c>
@@ -810,7 +825,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>28</v>
       </c>
@@ -830,7 +845,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -856,7 +871,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>28</v>
       </c>
